--- a/output/pdf_financials_xlsx/OTGO.H.xlsx
+++ b/output/pdf_financials_xlsx/OTGO.H.xlsx
@@ -1069,22 +1069,22 @@
         <v>0.199318</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.354335</v>
+        <v>-0.354335</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.366575</v>
+        <v>-1.366575</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.856841</v>
+        <v>-0.856841</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.011634</v>
+        <v>-1.011634</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.433744</v>
+        <v>-1.433744</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>15.362967</v>
+        <v>-15.362967</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.36252</v>
+        <v>-0.36252</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-0.482896</v>
@@ -1291,19 +1291,19 @@
         <v>0.199318</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.354335</v>
+        <v>-0.354335</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.366575</v>
+        <v>-1.366575</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.856841</v>
+        <v>-0.856841</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.011634</v>
+        <v>-1.011634</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.433744</v>
+        <v>-1.433744</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>12.100406</v>
@@ -1312,7 +1312,7 @@
         <v>-2.016276</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.36252</v>
+        <v>-0.36252</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-0.482896</v>
@@ -1420,22 +1420,22 @@
         <v>0.199318</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.354335</v>
+        <v>-0.354335</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.366575</v>
+        <v>-1.366575</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.856841</v>
+        <v>-0.856841</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.011634</v>
+        <v>-1.011634</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.433744</v>
+        <v>-1.433744</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>15.362967</v>
+        <v>-15.362967</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.36252</v>
+        <v>-0.36252</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-0.482896</v>
@@ -1551,19 +1551,19 @@
         <v>6.643933</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>8.858375000000001</v>
+        <v>-8.858375000000001</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>34.164375</v>
+        <v>-34.164375</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>42.84205</v>
+        <v>-42.84205</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-48.173048</v>
+        <v>48.173048</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-57.34976</v>
+        <v>57.34976</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>10.634464</v>
@@ -1572,7 +1572,7 @@
         <v>22.8839</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-18.126</v>
+        <v>18.126</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>24.1448</v>
@@ -1596,22 +1596,22 @@
         <v>0.199318</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.354335</v>
+        <v>-0.354335</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.366575</v>
+        <v>-1.366575</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.856841</v>
+        <v>-0.856841</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.011634</v>
+        <v>-1.011634</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.433744</v>
+        <v>-1.433744</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>15.362967</v>
+        <v>-15.362967</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.36252</v>
+        <v>-0.36252</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.482896</v>
@@ -1684,22 +1684,22 @@
         <v>0.199318</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.354335</v>
+        <v>-0.354335</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.366575</v>
+        <v>-1.366575</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.856841</v>
+        <v>-0.856841</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.011741</v>
+        <v>-1.011527</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.433882</v>
+        <v>-1.433606</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>15.363101</v>
+        <v>-15.362833</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.36252</v>
+        <v>-0.36252</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.482896</v>
@@ -1796,22 +1796,22 @@
         <v>0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -23681,10 +23681,10 @@
         </is>
       </c>
       <c r="N229" s="5" t="n">
-        <v>0.36252</v>
+        <v>-0.36252</v>
       </c>
       <c r="O229" s="5" t="n">
-        <v>0.482896</v>
+        <v>-0.482896</v>
       </c>
       <c r="P229" t="inlineStr">
         <is>
@@ -25551,13 +25551,13 @@
         </is>
       </c>
       <c r="J254" s="5" t="n">
-        <v>1.011634</v>
+        <v>-1.011634</v>
       </c>
       <c r="K254" s="5" t="n">
-        <v>1.433744</v>
+        <v>-1.433744</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>15.362967</v>
+        <v>-15.362967</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
@@ -25701,13 +25701,13 @@
         </is>
       </c>
       <c r="J256" s="5" t="n">
-        <v>1.030285</v>
+        <v>-1.030285</v>
       </c>
       <c r="K256" s="5" t="n">
-        <v>1.415093</v>
+        <v>-1.415093</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>15.362967</v>
+        <v>-15.362967</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
@@ -26742,10 +26742,10 @@
         </is>
       </c>
       <c r="I270" s="5" t="n">
-        <v>0.856841</v>
+        <v>-0.856841</v>
       </c>
       <c r="J270" s="5" t="n">
-        <v>1.011634</v>
+        <v>-1.011634</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -27112,13 +27112,13 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>0.354335</v>
+        <v>-0.354335</v>
       </c>
       <c r="H275" s="5" t="n">
-        <v>1.366575</v>
+        <v>-1.366575</v>
       </c>
       <c r="I275" s="5" t="n">
-        <v>0.856841</v>
+        <v>-0.856841</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OTGO.H.xlsx
+++ b/output/pdf_financials_xlsx/OTGO.H.xlsx
@@ -894,19 +894,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002095</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000944</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.007502</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007285</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1593,19 +1593,19 @@
         <v>-0.193253</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.199318</v>
+        <v>0.198518</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.354335</v>
+        <v>-0.35643</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.366575</v>
+        <v>-1.367519</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.856841</v>
+        <v>-0.864343</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.011634</v>
+        <v>-1.018919</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-1.433744</v>
@@ -1681,19 +1681,19 @@
         <v>-0.193253</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.199318</v>
+        <v>0.198518</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.354335</v>
+        <v>-0.35643</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.366575</v>
+        <v>-1.367519</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.856841</v>
+        <v>-0.864343</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.011527</v>
+        <v>-1.018812</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-1.433606</v>
@@ -1933,16 +1933,16 @@
         <v>0.856417</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.334566</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.132836</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.014912</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.008813</v>
       </c>
     </row>
     <row r="35">
@@ -2019,16 +2019,16 @@
         <v>0.856417</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.334566</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.132836</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.014912</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.008813</v>
       </c>
     </row>
     <row r="37">
@@ -2535,7 +2535,7 @@
         <v>0.3193</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.361387</v>
+        <v>0.026821</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -26644,7 +26644,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -27776,7 +27776,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">

--- a/output/pdf_financials_xlsx/OTGO.H.xlsx
+++ b/output/pdf_financials_xlsx/OTGO.H.xlsx
@@ -1306,10 +1306,10 @@
         <v>-1.433744</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12.100406</v>
+        <v>-3.262561</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-2.016276</v>
+        <v>-0.660861</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.36252</v>
@@ -1349,10 +1349,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>12.100406</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-2.016276</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -5282,10 +5282,10 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.470764</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.233152</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -14428,7 +14428,11 @@
           <t>Proceeds from private placement 7</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -15164,7 +15168,11 @@
           <t>Proceeds from private placement 6</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -15694,7 +15702,11 @@
           <t>Accretion expense 10</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -16452,7 +16464,11 @@
           <t>Accretion expense 11</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -24304,7 +24320,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -24341,10 +24361,10 @@
         </is>
       </c>
       <c r="L238" s="5" t="n">
-        <v>3.262561</v>
+        <v>-3.262561</v>
       </c>
       <c r="M238" s="5" t="n">
-        <v>0.660861</v>
+        <v>-0.660861</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -24680,7 +24700,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
